--- a/data/seed/portfolio/L-2025-3056/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-3056/vypiska_2026-07_09.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I130"/>
+  <dimension ref="A1:I158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -560,38 +560,38 @@
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>66289000</v>
+        <v>31203000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Ilhom Yog'och MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>288309624</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000869795623001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4364 ОТ 02.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №761</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>02.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -599,40 +599,40 @@
           <t>101</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n">
-        <v>29624000</v>
-      </c>
-      <c r="D11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n">
+        <v>42244000</v>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qog'oz AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>393321351</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000749277839001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №210/26 от 02.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9975</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>03.07.2026</t>
+          <t>06.07.2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -642,31 +642,31 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>57827000</v>
+        <v>12282000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №147/26 от 03.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8500</t>
         </is>
       </c>
     </row>
@@ -683,31 +683,31 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>94123000</v>
+        <v>11860000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №169/26 от 06.07.2026</t>
+          <t>Shartnoma №141/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -722,33 +722,33 @@
           <t>104</t>
         </is>
       </c>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n">
-        <v>57420000</v>
-      </c>
+      <c r="C14" s="2" t="n">
+        <v>126923000</v>
+      </c>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2744 за поставленный товар</t>
+          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTN. №188/26</t>
         </is>
       </c>
     </row>
@@ -764,39 +764,34 @@
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>35703000</v>
+        <v>199449000</v>
       </c>
       <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>209213775</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №200/26, QQS bilan</t>
+          <t>Iyun oyi uchun ish haqi, reestr №2210</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06.07.2026</t>
+          <t>07.07.2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -804,28 +799,33 @@
           <t>106</t>
         </is>
       </c>
-      <c r="C16" s="2" t="n">
-        <v>199449000</v>
-      </c>
-      <c r="D16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n">
+        <v>328336000</v>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Mahsulot uchun to'lov, shartnoma №96/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -840,33 +840,33 @@
           <t>107</t>
         </is>
       </c>
-      <c r="C17" s="2" t="n">
-        <v>25311000</v>
-      </c>
-      <c r="D17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n">
+        <v>31582000</v>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Bekobod Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>204611759</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000451239170001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №140/26</t>
+          <t>Предоплата за товар по договору №78/26 от 07.07.2026</t>
         </is>
       </c>
     </row>
@@ -881,40 +881,40 @@
           <t>108</t>
         </is>
       </c>
-      <c r="C18" s="2" t="n">
-        <v>16343000</v>
-      </c>
-      <c r="D18" s="2" t="n"/>
+      <c r="C18" s="2" t="n"/>
+      <c r="D18" s="2" t="n">
+        <v>115726000</v>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>206309480</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000498754332001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Арендная плата за июль 2026 г. по дог. №92/24</t>
+          <t>Tovar uchun to'lov, h/f №1668 08.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.07.2026</t>
+          <t>08.07.2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -923,32 +923,32 @@
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>66949000</v>
+        <v>16343000</v>
       </c>
       <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>331753518</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000825811918001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №181/26</t>
+          <t>Аренда помещения за июль, дог. №40/25</t>
         </is>
       </c>
     </row>
@@ -963,18 +963,23 @@
           <t>110</t>
         </is>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>140100000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>190336000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3056)</t>
+          <t>Farg'ona Metall Servis AJ</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>16307000257219405417</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -984,14 +989,14 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3056 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Shartnoma №282/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1001,38 +1006,38 @@
       </c>
       <c r="C21" s="2" t="n"/>
       <c r="D21" s="2" t="n">
-        <v>60008000</v>
+        <v>12987000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Jizzax Avto Ehtiyot MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>222203570</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000558838644001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1409 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №162/26 от 10.07.2026</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>13.07.2026</t>
+          <t>10.07.2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1040,33 +1045,28 @@
           <t>112</t>
         </is>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>46603000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>140100000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Andijon Moy MChJ</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>230600553</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3056)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000836314763001</t>
+          <t>16307000257219405417</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6239 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Kredit shartnomasi L-2025-3056 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
     </row>
@@ -1081,33 +1081,33 @@
           <t>113</t>
         </is>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>27304000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>50712000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Gulshan Mehmonxona MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>215339146</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000073790517001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №45/26</t>
+          <t>Shartnoma №275/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
@@ -1122,33 +1122,33 @@
           <t>114</t>
         </is>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>45819000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>11103000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №119/26, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №210/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1164,39 +1164,39 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>73547000</v>
+        <v>42425000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Gulshan Mehmonxona MChJ</t>
+          <t>Toshkent Qog'oz AJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>215339146</t>
+          <t>386998738</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000073790517001</t>
+          <t>20208000927035554001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №21/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №33/26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>14.07.2026</t>
+          <t>13.07.2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1204,40 +1204,40 @@
           <t>116</t>
         </is>
       </c>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n">
-        <v>94459000</v>
-      </c>
+      <c r="C26" s="2" t="n">
+        <v>83863000</v>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ishonch Yog' Zavodi AJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>314705096</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000002434007001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата по /ф №8089 за поставленный товар</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №161/26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>15.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1247,38 +1247,38 @@
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>189063000</v>
+        <v>18147000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №213/26 от 15.07.2026</t>
+          <t>Mahsulot uchun to'lov, shartnoma №122/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1286,40 +1286,40 @@
           <t>118</t>
         </is>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>245453000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>27198000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №268/26 от 16.07.2026</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1353,14 +1353,14 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>16.07.2026</t>
+          <t>14.07.2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1369,39 +1369,39 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>27198000</v>
+        <v>703074000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Toshkent Qog'oz AJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>386998738</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000927035554001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №220/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>21743000</v>
+        <v>28844000</v>
       </c>
       <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1435,14 +1435,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №6538</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №107/26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>17.07.2026</t>
+          <t>15.07.2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1451,39 +1451,39 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>132747000</v>
+        <v>36905000</v>
       </c>
       <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari MChJ</t>
+          <t>Shodlik Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>387869987</t>
+          <t>260055368</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000809270355001</t>
+          <t>20208000631476330001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4247</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №6661</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>16.07.2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1493,21 +1493,21 @@
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>75996000</v>
+        <v>37812000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1517,14 +1517,14 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №267/26 от 20.07.2026</t>
+          <t>Предоплата за товар по дог. №228/26 от 16.07.2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1532,40 +1532,40 @@
           <t>124</t>
         </is>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>23417000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>56820000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №209/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4250 17.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>20.07.2026</t>
+          <t>17.07.2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1573,33 +1573,33 @@
           <t>125</t>
         </is>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>23661000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>20193000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №102/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №268/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1614,33 +1614,33 @@
           <t>126</t>
         </is>
       </c>
-      <c r="C36" s="2" t="n">
-        <v>43305000</v>
-      </c>
-      <c r="D36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n">
+        <v>79307000</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №47/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №291/26, QQS 12%</t>
         </is>
       </c>
     </row>
@@ -1655,33 +1655,33 @@
           <t>127</t>
         </is>
       </c>
-      <c r="C37" s="2" t="n">
-        <v>59611000</v>
-      </c>
-      <c r="D37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n">
+        <v>40487000</v>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7773</t>
+          <t>Оплата по счет-фактуре №433 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1696,33 +1696,33 @@
           <t>128</t>
         </is>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>67954000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>21507000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Gulshan Mehmonxona MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>215339146</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000073790517001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4272</t>
+          <t>Оплата по с/ф №7858 за поставленный товар</t>
         </is>
       </c>
     </row>
@@ -1737,40 +1737,40 @@
           <t>129</t>
         </is>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>114757000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>14360000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Gulshan Mehmonxona MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>215339146</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000073790517001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №298/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5095</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>20.07.2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1778,40 +1778,40 @@
           <t>130</t>
         </is>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>181927000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>30907000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon XK</t>
+          <t>Toshkent Qog'oz AJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>204386720</t>
+          <t>386998738</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000768691754001</t>
+          <t>20208000927035554001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №227/26, НДС 12%</t>
+          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №218/26, QQS BILAN</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>22.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1819,40 +1819,40 @@
           <t>131</t>
         </is>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>27123000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>68698000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1814 21.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1860,40 +1860,40 @@
           <t>132</t>
         </is>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>29085000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>35173000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №143/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6950 21.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>24.07.2026</t>
+          <t>21.07.2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1902,39 +1902,39 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>210741000</v>
+        <v>365902000</v>
       </c>
       <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Shodlik Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>260055368</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000631476330001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №5200</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №59/26</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1944,21 +1944,21 @@
       </c>
       <c r="C44" s="2" t="n"/>
       <c r="D44" s="2" t="n">
-        <v>645976000</v>
+        <v>232717000</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Bekobod Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>204611759</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000451239170001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -1968,14 +1968,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9395</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8221</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1985,21 +1985,21 @@
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>149009000</v>
+        <v>14982000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2009,14 +2009,14 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №196/26 от 27.07.2026</t>
+          <t>Оплата по счет-фактуре №2695 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>22.07.2026</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2024,40 +2024,40 @@
           <t>136</t>
         </is>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>87256000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>26912000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Navro'z Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>314883096</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000428697956001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №6581 27.07.2026, QQS BILAN</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2067,21 +2067,21 @@
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>45709000</v>
+        <v>30102000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2091,14 +2091,14 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4896 от 27.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №2942 24.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>27.07.2026</t>
+          <t>24.07.2026</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2106,23 +2106,23 @@
           <t>138</t>
         </is>
       </c>
-      <c r="C48" s="2" t="n">
-        <v>10215000</v>
-      </c>
-      <c r="D48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n">
+        <v>11072000</v>
+      </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000278722854001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ЭЛЕКТРОЭНЕРГИЮ СОГЛАСНО СЧЕТУ</t>
+          <t>Yetkazilgan tovaruchun to'lov h/f №5338</t>
         </is>
       </c>
     </row>
@@ -2147,40 +2147,40 @@
           <t>139</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
-        <v>780563000</v>
-      </c>
-      <c r="D49" s="2" t="n"/>
+      <c r="C49" s="2" t="n"/>
+      <c r="D49" s="2" t="n">
+        <v>233477000</v>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №4897</t>
+          <t>Tovar uchun to'lov, h/f №7774 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2190,38 +2190,38 @@
       </c>
       <c r="C50" s="2" t="n"/>
       <c r="D50" s="2" t="n">
-        <v>163103000</v>
+        <v>96527000</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №287/26 от 31.07.2026</t>
+          <t>Shartnoma №258/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>31.07.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2229,35 +2229,40 @@
           <t>141</t>
         </is>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>96476000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Mahsulot uchun to'lov, shartnoma №177/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2267,21 +2272,21 @@
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>54119000</v>
+        <v>36725000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2291,14 +2296,14 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №238/26 от 03.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3668 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2308,38 +2313,38 @@
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>27751000</v>
+        <v>32434000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Oqtosh Yog'och XK</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>299261731</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000654835280001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №272/26 от 03.08.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1786 27.07.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>03.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2348,22 +2353,22 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>199072000</v>
+        <v>10215000</v>
       </c>
       <c r="D54" s="2" t="n"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Bog'ishamol Agro MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>293175351</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000682581191001</t>
+          <t>20208000896933213001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2373,14 +2378,14 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №164/26, QQS bilan</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>27.07.2026</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2388,40 +2393,40 @@
           <t>145</t>
         </is>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>53825000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>351921000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №141/26 от 05.08.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №156/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>28.07.2026</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2429,40 +2434,40 @@
           <t>146</t>
         </is>
       </c>
-      <c r="C56" s="2" t="n">
-        <v>47829000</v>
-      </c>
-      <c r="D56" s="2" t="n"/>
+      <c r="C56" s="2" t="n"/>
+      <c r="D56" s="2" t="n">
+        <v>12295000</v>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №185/26</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2848</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>05.08.2026</t>
+          <t>29.07.2026</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2471,17 +2476,22 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>209272000</v>
+        <v>53491000</v>
       </c>
       <c r="D57" s="2" t="n"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Chust Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>223753880</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000626148538001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2491,14 +2501,14 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №3045</t>
+          <t>Оплата за товары согласно счет-фактуре №4494</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2508,38 +2518,38 @@
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>101219000</v>
+        <v>65646000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2513 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №151/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>30.07.2026</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2549,21 +2559,21 @@
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>29993000</v>
+        <v>11939000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Bekobod Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>204611759</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000451239170001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -2573,14 +2583,14 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №314 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №4744 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2588,40 +2598,40 @@
           <t>150</t>
         </is>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>17148000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>137418000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish AJ</t>
+          <t>Bekobod Meva-Sabzavot AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>206309480</t>
+          <t>204611759</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000498754332001</t>
+          <t>20208000451239170001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по договору №92/24</t>
+          <t>Оплата за продукцию по дог. №162/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>31.07.2026</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2630,39 +2640,34 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>57032000</v>
+        <v>300000</v>
       </c>
       <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>209213775</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7251</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2670,35 +2675,40 @@
           <t>152</t>
         </is>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>140100000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>722213000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3056)</t>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>16307000257219405417</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3056 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Shartnoma №162/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2706,40 +2716,40 @@
           <t>153</t>
         </is>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>634910000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>72628000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chust Logistik AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>373709084</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000881830674001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №190/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №234/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2749,38 +2759,38 @@
       </c>
       <c r="C64" s="2" t="n"/>
       <c r="D64" s="2" t="n">
-        <v>30535000</v>
+        <v>72233000</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7594 от 11.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2136</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2788,40 +2798,40 @@
           <t>155</t>
         </is>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>56464000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>41565000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kattaqo'rg'on Qog'oz AJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>393321351</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000749277839001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №191/26 ОТ 11.08.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №95/26, НДС 12%</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2831,21 +2841,21 @@
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>538162000</v>
+        <v>40978000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2855,14 +2865,14 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №164/26 от 12.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2991</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>03.08.2026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2870,40 +2880,40 @@
           <t>157</t>
         </is>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>178407000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>16845000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №189/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №183/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2913,38 +2923,38 @@
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>160948000</v>
+        <v>71194000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bahor Un Mahsulotlari AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>380046117</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000964512391001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5288 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchunto'lov h/f №1181</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>12.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2952,40 +2962,40 @@
           <t>159</t>
         </is>
       </c>
-      <c r="C69" s="2" t="n">
-        <v>57676000</v>
-      </c>
-      <c r="D69" s="2" t="n"/>
+      <c r="C69" s="2" t="n"/>
+      <c r="D69" s="2" t="n">
+        <v>51973000</v>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №9533</t>
+          <t>Предоплата за товар по дог. №295/26 от 04.08.2026</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>04.08.2026</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2993,23 +3003,18 @@
           <t>160</t>
         </is>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>193891000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>209272000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Jizzax Avto Ehtiyot MChJ</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>222203570</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000558838644001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3019,14 +3024,14 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Shartnoma №195/26 bo'yicha oldindan to'lov</t>
+          <t>Ish haqi to'lovi iyul 2026 (plastik kartalarga)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3036,38 +3041,38 @@
       </c>
       <c r="C71" s="2" t="n"/>
       <c r="D71" s="2" t="n">
-        <v>35142000</v>
+        <v>135307000</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №295/26, НДС 12%</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №9438</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3075,40 +3080,40 @@
           <t>162</t>
         </is>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>33532000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>36923000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Omad Dori-Darmon XK</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>204386720</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000768691754001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №158/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №142/26</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>05.08.2026</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3117,39 +3122,39 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>28537000</v>
+        <v>96634000</v>
       </c>
       <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Buxoro Qurilish MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>374873533</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000875010835001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №179/26</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>07.08.2026</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3157,40 +3162,40 @@
           <t>164</t>
         </is>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>28537000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>47161000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>JShDS iyul oyi chun</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2615 07.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>17.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3198,40 +3203,40 @@
           <t>165</t>
         </is>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>424465000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>68511000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Oqtosh Yog'och XK</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>299261731</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000654835280001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №606</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5076 10.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3239,40 +3244,40 @@
           <t>166</t>
         </is>
       </c>
-      <c r="C76" s="2" t="n"/>
-      <c r="D76" s="2" t="n">
-        <v>53051000</v>
-      </c>
+      <c r="C76" s="2" t="n">
+        <v>17148000</v>
+      </c>
+      <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ishonch Yog' Zavodi AJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>314705096</t>
+          <t>331753518</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000002434007001</t>
+          <t>20208000825811918001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2196 от 19.08.2026, в т.ч. НДС 12%</t>
+          <t>Арендная плата за август 2026 г. по договору №40/25</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>10.08.2026</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3280,40 +3285,35 @@
           <t>167</t>
         </is>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>28753000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>140100000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Navro'z Farm Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>314883096</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3056)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000428697956001</t>
+          <t>16307000257219405417</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №130</t>
+          <t>Kredit shartnomasi L-2025-3056 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>19.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3321,40 +3321,40 @@
           <t>168</t>
         </is>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>143372000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>87430000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №206/26 от 19.08.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9371 11.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>11.08.2026</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3364,38 +3364,38 @@
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>34099000</v>
+        <v>73077000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Bekobod Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>270509640</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000243400735001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6892 от 21.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №219/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>21.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3403,40 +3403,40 @@
           <t>170</t>
         </is>
       </c>
-      <c r="C80" s="2" t="n">
-        <v>28434000</v>
-      </c>
-      <c r="D80" s="2" t="n"/>
+      <c r="C80" s="2" t="n"/>
+      <c r="D80" s="2" t="n">
+        <v>496404000</v>
+      </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2141 12.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>12.08.2026</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3446,38 +3446,38 @@
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>100825000</v>
+        <v>37242000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Lazzat Qurilish MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>384989930</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000404054056001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9590</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8199 12.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>13.08.2026</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3487,38 +3487,38 @@
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>55367000</v>
+        <v>66562000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9228 24.08.2026, QQS bilan</t>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №3152</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3526,40 +3526,40 @@
           <t>173</t>
         </is>
       </c>
-      <c r="C83" s="2" t="n"/>
-      <c r="D83" s="2" t="n">
-        <v>51051000</v>
-      </c>
+      <c r="C83" s="2" t="n">
+        <v>28537000</v>
+      </c>
+      <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Andijon Moy MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>230600553</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000836314763001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №102/26, НДС 12%</t>
+          <t>IJTIMOIY SOLIQ IYUL 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>14.08.2026</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3567,40 +3567,40 @@
           <t>174</t>
         </is>
       </c>
-      <c r="C84" s="2" t="n"/>
-      <c r="D84" s="2" t="n">
-        <v>49599000</v>
-      </c>
+      <c r="C84" s="2" t="n">
+        <v>28537000</v>
+      </c>
+      <c r="D84" s="2" t="n"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2971 за поставленный товар</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3608,40 +3608,40 @@
           <t>175</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>38728000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>24841000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №816 за поставленный товар</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №295/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>17.08.2026</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3650,39 +3650,39 @@
         </is>
       </c>
       <c r="C86" s="2" t="n">
-        <v>10718000</v>
+        <v>27520000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000278722854001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Tovarlar uchun to'lov h/f №8129</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>24.08.2026</t>
+          <t>18.08.2026</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,39 +3691,39 @@
         </is>
       </c>
       <c r="C87" s="2" t="n">
-        <v>195113000</v>
+        <v>189453000</v>
       </c>
       <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bog'ishamol Ip-Kalava AJ</t>
+          <t>Toshkent Qog'oz AJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>323237538</t>
+          <t>386998738</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000016261485001</t>
+          <t>20208000927035554001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №133/26</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №165/26</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>25.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3731,40 +3731,40 @@
           <t>178</t>
         </is>
       </c>
-      <c r="C88" s="2" t="n">
-        <v>97442000</v>
-      </c>
-      <c r="D88" s="2" t="n"/>
+      <c r="C88" s="2" t="n"/>
+      <c r="D88" s="2" t="n">
+        <v>74302000</v>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bog'ishamol Agro MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>293175351</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000682581191001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7741</t>
+          <t>Shartnoma №25/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>26.08.2026</t>
+          <t>19.08.2026</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3772,40 +3772,40 @@
           <t>179</t>
         </is>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>369899000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>173185000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Buxoro Qurilish MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>374873533</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000875010835001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №6252 26.08.2026, QQS bilan</t>
+          <t>Tovarlar uchun to'lov h/f №7250</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>27.08.2026</t>
+          <t>20.08.2026</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3813,40 +3813,40 @@
           <t>180</t>
         </is>
       </c>
-      <c r="C90" s="2" t="n"/>
-      <c r="D90" s="2" t="n">
-        <v>30973000</v>
-      </c>
+      <c r="C90" s="2" t="n">
+        <v>485082000</v>
+      </c>
+      <c r="D90" s="2" t="n"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Shartnoma №93/26 bo'yicha oldindan to'lov</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №82/26</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>21.08.2026</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3856,38 +3856,38 @@
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>65149000</v>
+        <v>40250000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Ilhom Yog'och MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>288309624</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000869795623001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9037 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8959</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3897,38 +3897,38 @@
       </c>
       <c r="C92" s="2" t="n"/>
       <c r="D92" s="2" t="n">
-        <v>54454000</v>
+        <v>215992000</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2343 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №254/26 от 24.08.2026</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>31.08.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3937,34 +3937,39 @@
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>300000</v>
+        <v>10718000</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000896933213001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за август</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3972,40 +3977,40 @@
           <t>184</t>
         </is>
       </c>
-      <c r="C94" s="2" t="n"/>
-      <c r="D94" s="2" t="n">
-        <v>279650000</v>
-      </c>
+      <c r="C94" s="2" t="n">
+        <v>20364000</v>
+      </c>
+      <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lazzat Qurilish MChJ</t>
+          <t>Omad Tekstil MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>384989930</t>
+          <t>325692425</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000404054056001</t>
+          <t>20208000704248372001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4937 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №1074</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>02.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -4013,40 +4018,40 @@
           <t>185</t>
         </is>
       </c>
-      <c r="C95" s="2" t="n"/>
-      <c r="D95" s="2" t="n">
-        <v>279125000</v>
-      </c>
+      <c r="C95" s="2" t="n">
+        <v>24295000</v>
+      </c>
+      <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sarbon Savdo MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>372992617</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000116548352001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №126/26 от 02.09.2026</t>
+          <t>Оплата за упаковочные материалы, с/ф №9049</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -4054,40 +4059,40 @@
           <t>186</t>
         </is>
       </c>
-      <c r="C96" s="2" t="n"/>
-      <c r="D96" s="2" t="n">
-        <v>47812000</v>
-      </c>
+      <c r="C96" s="2" t="n">
+        <v>29443000</v>
+      </c>
+      <c r="D96" s="2" t="n"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Navro'z Farm Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>314883096</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000428697956001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6811 за поставленный товар</t>
+          <t>QQS iyul 2026 uchun</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>04.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -4096,34 +4101,39 @@
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>212542000</v>
+        <v>53065000</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Shodlik Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>260055368</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000631476330001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №138/26</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>24.08.2026</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -4131,40 +4141,40 @@
           <t>188</t>
         </is>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>105069000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>576297000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №161/26 от 07.09.2026</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №140/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>28.08.2026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -4173,39 +4183,39 @@
         </is>
       </c>
       <c r="C99" s="2" t="n">
-        <v>17416000</v>
+        <v>77421000</v>
       </c>
       <c r="D99" s="2" t="n"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Zarafshon Qurilish AJ</t>
+          <t>Shodlik Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>206309480</t>
+          <t>260055368</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000498754332001</t>
+          <t>20208000631476330001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov sentyabr</t>
+          <t>Оплата за упаковочные материалы, с/ф №5638</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>07.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -4213,40 +4223,40 @@
           <t>190</t>
         </is>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>106515000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>38586000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari MChJ</t>
+          <t>Ilhom Yog'och MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>387869987</t>
+          <t>288309624</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000809270355001</t>
+          <t>20208000869795623001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГ. №208/26 ОТ 07.09.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4189 31.08.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>08.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -4255,39 +4265,34 @@
         </is>
       </c>
       <c r="C101" s="2" t="n">
-        <v>99958000</v>
+        <v>300000</v>
       </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>209213775</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №987</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>09.09.2026</t>
+          <t>31.08.2026</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -4295,40 +4300,40 @@
           <t>192</t>
         </is>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>77945000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>124559000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Sarbon Savdo MChJ</t>
+          <t>Buxoro Qurilish MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>372992617</t>
+          <t>374873533</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000116548352001</t>
+          <t>20208000875010835001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6583 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №9651</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>01.09.2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4338,38 +4343,38 @@
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n">
-        <v>83754000</v>
+        <v>102564000</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №1413 ОТ 10.09.2026, В Т.Ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №130/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4377,35 +4382,40 @@
           <t>194</t>
         </is>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>140100000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>39802000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-3056)</t>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>16307000257219405417</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-3056 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6161 02.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>11.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4413,40 +4423,40 @@
           <t>195</t>
         </is>
       </c>
-      <c r="C105" s="2" t="n">
-        <v>76197000</v>
-      </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="C105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>20370000</v>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Bog'ishamol Agro MChJ</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>293175351</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000682581191001</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4383</t>
+          <t>Mahsulot uchun to'lov, shartnoma №21/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4456,21 +4466,21 @@
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>238704000</v>
+        <v>101696000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jizzax Avto Ehtiyot MChJ</t>
+          <t>Oqtosh Yog'och XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>222203570</t>
+          <t>299261731</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000558838644001</t>
+          <t>20208000654835280001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4480,14 +4490,14 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №210/26 ОТ 14.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №33/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>03.09.2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4497,38 +4507,38 @@
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>110257000</v>
+        <v>45967000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Jizzax Avto Ehtiyot MChJ</t>
+          <t>Ishonch Savdo MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>222203570</t>
+          <t>220357005</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000558838644001</t>
+          <t>20208000883864412001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №3484 14.09.2026, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8856</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4538,38 +4548,38 @@
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>99953000</v>
+        <v>103023000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5475 от 14.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №116/26 от 04.09.2026</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>14.09.2026</t>
+          <t>04.09.2026</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4578,39 +4588,34 @@
         </is>
       </c>
       <c r="C109" s="2" t="n">
-        <v>162454000</v>
+        <v>212542000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>209213775</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №278/26 от 14.09.2026, НДС 12%</t>
+          <t>ISH HAQI TO'LOVI AVGUST 2026 (PLASTIK KARTALARGA)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4618,40 +4623,40 @@
           <t>200</t>
         </is>
       </c>
-      <c r="C110" s="2" t="n">
-        <v>28983000</v>
-      </c>
-      <c r="D110" s="2" t="n"/>
+      <c r="C110" s="2" t="n"/>
+      <c r="D110" s="2" t="n">
+        <v>102970000</v>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Предоплата за товар по договору №223/26 от 07.09.2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4659,40 +4664,40 @@
           <t>201</t>
         </is>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>28983000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>42866000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Oqtosh Yog'och XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>299261731</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000654835280001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7555</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>15.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4700,40 +4705,40 @@
           <t>202</t>
         </is>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>175661000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>35682000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Oqtosh Yog'och XK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>299261731</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000654835280001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №203/26 от 15.09.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2932</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>16.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4743,38 +4748,38 @@
       </c>
       <c r="C113" s="2" t="n"/>
       <c r="D113" s="2" t="n">
-        <v>288517000</v>
+        <v>33492000</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №66/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №169/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4782,40 +4787,40 @@
           <t>204</t>
         </is>
       </c>
-      <c r="C114" s="2" t="n"/>
-      <c r="D114" s="2" t="n">
-        <v>100616000</v>
-      </c>
+      <c r="C114" s="2" t="n">
+        <v>43871000</v>
+      </c>
+      <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Shodlik Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>260055368</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000631476330001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7442 от 17.09.2026, в т.ч. НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №79/26</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>17.09.2026</t>
+          <t>07.09.2026</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4824,39 +4829,39 @@
         </is>
       </c>
       <c r="C115" s="2" t="n">
-        <v>244549000</v>
+        <v>151602000</v>
       </c>
       <c r="D115" s="2" t="n"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Olmaliq Yog'och AJ</t>
+          <t>Toshkent Qog'oz AJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>209213775</t>
+          <t>386998738</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000085049305001</t>
+          <t>20208000927035554001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №120/26</t>
+          <t>Предоплата за материалы по договору №53/26</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>18.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4865,39 +4870,39 @@
         </is>
       </c>
       <c r="C116" s="2" t="n">
-        <v>111989000</v>
+        <v>17416000</v>
       </c>
       <c r="D116" s="2" t="n"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Qurilish MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>387869987</t>
+          <t>331753518</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000809270355001</t>
+          <t>20208000825811918001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №78/26</t>
+          <t>Bino ijarasi uchun to'lov sentyabr</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>08.09.2026</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4905,40 +4910,40 @@
           <t>207</t>
         </is>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>170049000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>140535000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>389434380</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000179557186001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №1134 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №210/26, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4948,21 +4953,21 @@
       </c>
       <c r="C118" s="2" t="n"/>
       <c r="D118" s="2" t="n">
-        <v>98263000</v>
+        <v>118918000</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jizzax Avto Ehtiyot MChJ</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>222203570</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000558838644001</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4972,14 +4977,14 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №288/26 от 21.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №392 09.09.2026, QQS bilan</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>09.09.2026</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4989,38 +4994,38 @@
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>52477000</v>
+        <v>46973000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7584 от 22.09.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №144/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -5028,40 +5033,40 @@
           <t>210</t>
         </is>
       </c>
-      <c r="C120" s="2" t="n">
-        <v>28649000</v>
-      </c>
-      <c r="D120" s="2" t="n"/>
+      <c r="C120" s="2" t="n"/>
+      <c r="D120" s="2" t="n">
+        <v>183734000</v>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Mahsulot uchun to'lov, shartnoma №164/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -5071,38 +5076,38 @@
       </c>
       <c r="C121" s="2" t="n"/>
       <c r="D121" s="2" t="n">
-        <v>197910000</v>
+        <v>44763000</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Sarbon Savdo MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>372992617</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000116548352001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2212</t>
+          <t>Оплата по с/ф №6678 за поставленный товар</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>10.09.2026</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -5111,39 +5116,34 @@
         </is>
       </c>
       <c r="C122" s="2" t="n">
-        <v>302787000</v>
+        <v>140100000</v>
       </c>
       <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Nukus Yog' Zavodi MChJ</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>239967698</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-3056)</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000868718601001</t>
+          <t>16307000257219405417</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №110/26</t>
+          <t>Kredit shartnomasi L-2025-3056 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>11.09.2026</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -5153,38 +5153,38 @@
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>157276000</v>
+        <v>20816000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Toshkent Sut Mahsulotlari MChJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>279170184</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000212453108001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2474</t>
+          <t>Mahsulot uchun to'lov, shartn. №178/26, QQS 12%</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -5192,23 +5192,23 @@
           <t>214</t>
         </is>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>10885000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>87850000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Saodat Avto Ehtiyot XK</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>317018452</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000278722854001</t>
+          <t>20208000245310867001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5218,14 +5218,14 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №5555</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -5233,40 +5233,40 @@
           <t>215</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v>59045000</v>
-      </c>
-      <c r="D125" s="2" t="n"/>
+      <c r="C125" s="2" t="n"/>
+      <c r="D125" s="2" t="n">
+        <v>22357000</v>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bog'ishamol Ip-Kalava AJ</t>
+          <t>Farg'ona Metall Servis AJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>323237538</t>
+          <t>337195583</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000016261485001</t>
+          <t>20208000679666352001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №89/26</t>
+          <t>SHARTNOMA №91/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>28.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -5275,39 +5275,39 @@
         </is>
       </c>
       <c r="C126" s="2" t="n">
-        <v>82108000</v>
+        <v>28983000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>387869987</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000809270355001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №153/26 от 28.09.2026, НДС 12%</t>
+          <t>IJTIMOIY SOLIQ AVGUST 2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>29.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -5316,39 +5316,39 @@
         </is>
       </c>
       <c r="C127" s="2" t="n">
-        <v>515261000</v>
+        <v>28983000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Nukus Yog' Zavodi MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>239967698</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000868718601001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №261/26</t>
+          <t>Jismoniy shaxslar daromad solg'i avgust 2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>30.09.2026</t>
+          <t>14.09.2026</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -5357,53 +5357,1201 @@
         </is>
       </c>
       <c r="C128" s="2" t="n">
-        <v>300000</v>
+        <v>47107000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Buxoro Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>374873533</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000875010835001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>TOVARLAR UCHUN TO'LOV H/F №4712</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Jami aylanma:</t>
-        </is>
-      </c>
-      <c r="C129" s="4" t="n">
-        <v>7040570000</v>
-      </c>
-      <c r="D129" s="4" t="n">
-        <v>7017070000</v>
+          <t>14.09.2026</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="n">
+        <v>54763000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Buxoro Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>374873533</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>20208000875010835001</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Предоплата за материалы по договору №255/26</t>
+        </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="n"/>
+      <c r="D130" s="2" t="n">
+        <v>122915000</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №3028 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>15.09.2026</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="n"/>
+      <c r="D131" s="2" t="n">
+        <v>33207000</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №2972 15.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>41864000</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>220357005</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>20208000883864412001</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Shartnoma №26/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="n">
+        <v>40824000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Chust Moy MChJ</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>223753880</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>20208000626148538001</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №1854</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>16.09.2026</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="n">
+        <v>702508000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Tong Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>389434380</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>20208000179557186001</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №120/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>88331000</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Shartnoma №42/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>17.09.2026</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>46058000</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Shodlik Un Mahsulotlari AJ</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>298993064</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>20208000405405623001</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №535 17.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>97776000</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №56/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>48886000</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>220357005</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>20208000883864412001</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Mahsulot uchun to'lov, shartnoma №38/26, QQS 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="n"/>
+      <c r="D139" s="2" t="n">
+        <v>20580000</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>220357005</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>20208000883864412001</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №4153</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="n">
+        <v>28320000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>201122905</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>QQS avgust 2026 uchun</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="n">
+        <v>70717000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Tong Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>389434380</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>20208000179557186001</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Оплата за товары согласно счет-фактуре №8015</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="n">
+        <v>152866000</v>
+      </c>
+      <c r="D142" s="2" t="n"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Tong Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>389434380</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>20208000179557186001</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №291/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>21.09.2026</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="n">
+        <v>426459000</v>
+      </c>
+      <c r="D143" s="2" t="n"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Buxoro Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>374873533</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>20208000875010835001</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Tovarlar uchun to'lov h/f №3416</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>22.09.2026</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>119141000</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>220357005</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>20208000883864412001</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Оплата за продукцию по дог. №105/26, НДС 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>23.09.2026</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>42584000</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="n">
+        <v>10885000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Hududiy elektr tarmoqlari AJ</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>200933985</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>20208000896933213001</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Elektr energiyasi uchun to'lov sentyabr</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>24.09.2026</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="n">
+        <v>50961000</v>
+      </c>
+      <c r="D147" s="2" t="n"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Toshkent Qog'oz AJ</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>386998738</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>20208000927035554001</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Оплата за транспортные услуги по договору №283/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="n"/>
+      <c r="D148" s="2" t="n">
+        <v>67005000</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Предоплата за товар по дог. №227/26 от 25.09.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>26985000</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2396</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>25.09.2026</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>19160000</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №3736 25.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="n"/>
+      <c r="D151" s="2" t="n">
+        <v>178412000</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>220357005</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>20208000883864412001</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №3219</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="n"/>
+      <c r="D152" s="2" t="n">
+        <v>84317000</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Ishonch Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>220357005</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>20208000883864412001</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>01204</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Yetkazilgan tovar uchun to'lov h/f №6954</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>28.09.2026</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="n"/>
+      <c r="D153" s="2" t="n">
+        <v>72447000</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Ilhom Yog'och MChJ</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>288309624</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>20208000869795623001</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, hisob-faktura №776 28.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="n"/>
+      <c r="D154" s="2" t="n">
+        <v>96528000</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Saodat Avto Ehtiyot XK</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>317018452</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>20208000245310867001</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>01153</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Tovar uchun to'lov, h/f №5903 29.09.2026, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>29.09.2026</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="n">
+        <v>67581000</v>
+      </c>
+      <c r="D155" s="2" t="n"/>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Tong Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>389434380</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>20208000179557186001</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>00962</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Xom ashyo uchun to'lov, shartnoma №10/26, QQS bilan</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>30.09.2026</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D156" s="2" t="n"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Navbahor Bank ATB</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>45994000900000001001</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>01121</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Bank xizmati uchun komissiya</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Jami aylanma:</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="n">
+        <v>7079832000</v>
+      </c>
+      <c r="D157" s="4" t="n">
+        <v>7056332000</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
           <t>Davr oxiridagi qoldiq:</t>
         </is>
       </c>
-      <c r="C130" s="4" t="n">
+      <c r="C158" s="4" t="n">
         <v>471500000</v>
       </c>
-      <c r="D130" s="4" t="n"/>
+      <c r="D158" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
